--- a/examples/wangetal2018/out/NetworkFiles/AC_1.0_b_network_design.xlsx
+++ b/examples/wangetal2018/out/NetworkFiles/AC_1.0_b_network_design.xlsx
@@ -8,18 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="PIPES" sheetId="1" r:id="rId1"/>
-    <sheet name="NODES" sheetId="2" r:id="rId2"/>
-    <sheet name="COMPRESSORS" sheetId="3" r:id="rId3"/>
-    <sheet name="SUPPLY" sheetId="4" r:id="rId4"/>
-    <sheet name="DEMAND" sheetId="5" r:id="rId5"/>
-    <sheet name="COMPOSITION" sheetId="6" r:id="rId6"/>
+    <sheet name="SUPPLY" sheetId="2" r:id="rId2"/>
+    <sheet name="DEMAND" sheetId="3" r:id="rId3"/>
+    <sheet name="COMPOSITION" sheetId="4" r:id="rId4"/>
+    <sheet name="NODES" sheetId="5" r:id="rId5"/>
+    <sheet name="COMPRESSORS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="95">
   <si>
     <t>pipe_name</t>
   </si>
@@ -42,207 +42,231 @@
     <t>thickness_mm</t>
   </si>
   <si>
-    <t>steel_grade</t>
+    <t>rating_code</t>
   </si>
   <si>
     <t>PI01_0</t>
   </si>
   <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>X60</t>
+  </si>
+  <si>
     <t>PI01_1</t>
   </si>
   <si>
+    <t>N01_1</t>
+  </si>
+  <si>
     <t>PI01_pre_C_0_0</t>
   </si>
   <si>
+    <t>N_pre_C_0_0</t>
+  </si>
+  <si>
     <t>PI01_remaining</t>
   </si>
   <si>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
     <t>PI02_0</t>
   </si>
   <si>
+    <t>N02_0</t>
+  </si>
+  <si>
     <t>PI02</t>
   </si>
   <si>
+    <t>N03</t>
+  </si>
+  <si>
     <t>PI03_0</t>
   </si>
   <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
     <t>PI03</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI04_0_remaining</t>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0</t>
+  </si>
+  <si>
+    <t>N04_0</t>
   </si>
   <si>
     <t>PI04_1</t>
   </si>
   <si>
-    <t>PI04</t>
-  </si>
-  <si>
-    <t>PI05_0_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>PI05_0_remaining</t>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>PI04_remaining</t>
+  </si>
+  <si>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0</t>
+  </si>
+  <si>
+    <t>N05_0</t>
   </si>
   <si>
     <t>PI05_1</t>
   </si>
   <si>
+    <t>N05_1</t>
+  </si>
+  <si>
     <t>PI05</t>
   </si>
   <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1</t>
   </si>
   <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1</t>
   </si>
   <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1</t>
   </si>
   <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
     <t>PI09_0</t>
   </si>
   <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1</t>
   </si>
   <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>X60</t>
+    <t>supply_name</t>
   </si>
   <si>
     <t>node_name</t>
   </si>
   <si>
+    <t>pressure_mpa_g</t>
+  </si>
+  <si>
+    <t>flowrate_MW</t>
+  </si>
+  <si>
+    <t>blend</t>
+  </si>
+  <si>
+    <t>supply1</t>
+  </si>
+  <si>
+    <t>demand_name</t>
+  </si>
+  <si>
+    <t>N13</t>
+  </si>
+  <si>
+    <t>SPECIES</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
     <t>p_max_mpa_g</t>
   </si>
   <si>
@@ -273,9 +297,6 @@
     <t>C_1_0</t>
   </si>
   <si>
-    <t>C_1_1</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -283,52 +304,14 @@
   </si>
   <si>
     <t>CS3</t>
-  </si>
-  <si>
-    <t>supply_name</t>
-  </si>
-  <si>
-    <t>pressure_mpa_g</t>
-  </si>
-  <si>
-    <t>flowrate_MW</t>
-  </si>
-  <si>
-    <t>supply1</t>
-  </si>
-  <si>
-    <t>demand_name</t>
-  </si>
-  <si>
-    <t>N13</t>
-  </si>
-  <si>
-    <t>SPECIES</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>H2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -344,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -352,30 +335,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,32 +635,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -704,10 +669,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>641.35</v>
@@ -722,18 +687,18 @@
         <v>9.525</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>641.35</v>
@@ -748,18 +713,18 @@
         <v>9.525</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>641.35</v>
@@ -774,18 +739,18 @@
         <v>9.525</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>641.35</v>
@@ -800,18 +765,18 @@
         <v>9.525</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>641.35</v>
@@ -826,18 +791,18 @@
         <v>9.525</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>641.35</v>
@@ -852,18 +817,18 @@
         <v>9.525</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>641.35</v>
@@ -878,18 +843,18 @@
         <v>9.525</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>641.35</v>
@@ -904,24 +869,24 @@
         <v>9.525</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>641.35</v>
       </c>
       <c r="E10">
-        <v>11.83333333333334</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="F10">
         <v>0.012</v>
@@ -930,24 +895,24 @@
         <v>9.525</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>641.35</v>
       </c>
       <c r="E11">
-        <v>4.333333333333329</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="F11">
         <v>0.012</v>
@@ -956,24 +921,24 @@
         <v>9.525</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>641.35</v>
       </c>
       <c r="E12">
-        <v>16.16666666666667</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="F12">
         <v>0.012</v>
@@ -982,24 +947,24 @@
         <v>9.525</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D13">
         <v>641.35</v>
       </c>
       <c r="E13">
-        <v>16.16666666666667</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="F13">
         <v>0.012</v>
@@ -1008,24 +973,24 @@
         <v>9.525</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D14">
         <v>641.35</v>
       </c>
       <c r="E14">
-        <v>6.666666666666671</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="F14">
         <v>0.012</v>
@@ -1034,24 +999,24 @@
         <v>9.525</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>641.35</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="F15">
         <v>0.012</v>
@@ -1060,18 +1025,18 @@
         <v>9.525</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>641.35</v>
@@ -1086,18 +1051,18 @@
         <v>9.525</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D17">
         <v>641.35</v>
@@ -1112,18 +1077,18 @@
         <v>9.525</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>641.35</v>
@@ -1138,18 +1103,18 @@
         <v>9.525</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D19">
         <v>641.35</v>
@@ -1164,18 +1129,18 @@
         <v>9.525</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D20">
         <v>641.35</v>
@@ -1190,24 +1155,24 @@
         <v>9.525</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>641.35</v>
       </c>
       <c r="E21">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="F21">
         <v>0.012</v>
@@ -1216,18 +1181,18 @@
         <v>9.525</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
         <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
       </c>
       <c r="D22">
         <v>641.35</v>
@@ -1242,18 +1207,18 @@
         <v>9.525</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D23">
         <v>641.35</v>
@@ -1268,18 +1233,18 @@
         <v>9.525</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24">
         <v>641.35</v>
@@ -1294,18 +1259,18 @@
         <v>9.525</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D25">
         <v>641.35</v>
@@ -1320,18 +1285,18 @@
         <v>9.525</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>641.35</v>
@@ -1346,18 +1311,18 @@
         <v>9.525</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D27">
         <v>641.35</v>
@@ -1372,18 +1337,18 @@
         <v>9.525</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D28">
         <v>641.35</v>
@@ -1398,33 +1363,7 @@
         <v>9.525</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29">
-        <v>641.35</v>
-      </c>
-      <c r="E29">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="F29">
-        <v>0.012</v>
-      </c>
-      <c r="G29">
-        <v>9.525</v>
-      </c>
-      <c r="H29" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1434,303 +1373,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36">
-        <v>8.758481331682836</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37">
-        <v>8.758481331682836</v>
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1740,215 +1414,51 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>1150.5204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3">
+        <v>2991.353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0.78</v>
-      </c>
-      <c r="H2">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E3">
-        <v>12.5</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>0.78</v>
-      </c>
-      <c r="H3">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>83</v>
-      </c>
       <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0.78</v>
-      </c>
-      <c r="H4">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0.78</v>
-      </c>
-      <c r="H5">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E6">
-        <v>12.5</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>0.78</v>
-      </c>
-      <c r="H6">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" t="s">
         <v>69</v>
       </c>
-      <c r="C7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0.78</v>
-      </c>
-      <c r="H7">
-        <v>0.357</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="E8">
-        <v>12.5</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>0.78</v>
-      </c>
-      <c r="H8">
-        <v>0.357</v>
+      <c r="C4">
+        <v>2301.0408</v>
       </c>
     </row>
   </sheetData>
@@ -1958,32 +1468,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2">
-        <v>8.699999999999999</v>
+        <v>80</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1993,51 +1502,287 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>44</v>
       </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2">
-        <v>1150.5204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3">
-        <v>2991.353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4">
-        <v>2301.0408</v>
+      <c r="B21">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34">
+        <v>8.758481331682836</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35">
+        <v>8.758481331682836</v>
       </c>
     </row>
   </sheetData>
@@ -2047,31 +1792,189 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.78</v>
+      </c>
+      <c r="H2">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E3">
+        <v>12.5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.78</v>
+      </c>
+      <c r="H3">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.78</v>
+      </c>
+      <c r="H4">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E5">
+        <v>12.5</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.78</v>
+      </c>
+      <c r="H5">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0.78</v>
+      </c>
+      <c r="H6">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3">
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>8.758481331682836</v>
+      </c>
+      <c r="E7">
+        <v>12.5</v>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.78</v>
+      </c>
+      <c r="H7">
+        <v>0.357</v>
       </c>
     </row>
   </sheetData>
